--- a/ig/DM-JUILLET-2026/ValueSet-JDV-J238-TypeOffre-ROR.xlsx
+++ b/ig/DM-JUILLET-2026/ValueSet-JDV-J238-TypeOffre-ROR.xlsx
@@ -1932,7 +1932,7 @@
     <t>320</t>
   </si>
   <si>
-    <t>Structure de relayage au domicile</t>
+    <t>Offre de relayage au domicile</t>
   </si>
   <si>
     <t/>
